--- a/test_cases/regf2_testbench.xlsx
+++ b/test_cases/regf2_testbench.xlsx
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
         <v>0.15</v>
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H2" s="4">
         <v>0.11</v>

--- a/test_cases/regf2_testbench.xlsx
+++ b/test_cases/regf2_testbench.xlsx
@@ -51,7 +51,7 @@
     <t>TimeSeries_1</t>
   </si>
   <si>
-    <t>disturbance_profile_15.xlsx</t>
+    <t>disturbance_profile.xlsx</t>
   </si>
   <si>
     <t>PLBVF</t>

--- a/test_cases/regf2_testbench.xlsx
+++ b/test_cases/regf2_testbench.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="80">
   <si>
     <t>name</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Tr</t>
+  </si>
+  <si>
+    <t>Pmax</t>
   </si>
   <si>
     <t>REGF2_1</t>
@@ -1164,7 +1167,7 @@
         <v>34.5</v>
       </c>
       <c r="K2">
-        <v>0.01938</v>
+        <v>0.2</v>
       </c>
       <c r="L2">
         <v>0.2</v>
@@ -1535,7 +1538,9 @@
       <c r="O1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="P1" s="3"/>
+      <c r="P1" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
@@ -1548,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
@@ -1583,7 +1588,9 @@
       <c r="O2" s="4">
         <v>0.005</v>
       </c>
-      <c r="P2" s="3"/>
+      <c r="P2" s="3">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -2789,13 +2796,13 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>

--- a/test_cases/regf2_testbench.xlsx
+++ b/test_cases/regf2_testbench.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
   <si>
     <t>name</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>BusROCOF_1</t>
+  </si>
+  <si>
+    <t>BusROCOF_2</t>
   </si>
 </sst>
 </file>
@@ -1377,10 +1380,10 @@
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2832,18 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
